--- a/supporting_material/experiments/template/template.xlsx
+++ b/supporting_material/experiments/template/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adrianomartinelli/projects/delt-hit/supporting_material/experiments/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18962022-68DE-D04A-93B1-CCC6D3EB3216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06E3314-4FEE-BB40-A481-82BA60057587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1520" yWindow="1600" windowWidth="27220" windowHeight="17080" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5341,12 +5341,6 @@
     <t>[CX3:1](=[O:2])[OX2;H1].[N;$([N;H1,H2]),$([N;H3]);!$([N;H1,H2][S]);!$([NX3][CX3](=[OX1])[#6]);!$([NX3][CX3](=[OX1])[OX2]):4]&gt;&gt;[CX3:1](=[O:2])[N:4]</t>
   </si>
   <si>
-    <t>template</t>
-  </si>
-  <si>
-    <t>experiments</t>
-  </si>
-  <si>
     <t>A. Smith</t>
   </si>
   <si>
@@ -5369,6 +5363,12 @@
   </si>
   <si>
     <t>E</t>
+  </si>
+  <si>
+    <t>./</t>
+  </si>
+  <si>
+    <t>campaign</t>
   </si>
 </sst>
 </file>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1765</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -6255,7 +6255,7 @@
         <v>25</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -6263,7 +6263,7 @@
         <v>26</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1766</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -6307,7 +6307,7 @@
         <v>60</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>19</v>
@@ -6321,7 +6321,7 @@
         <v>64</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C2" s="48">
         <v>45561</v>
@@ -6342,7 +6342,7 @@
         <v>65</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C3" s="48">
         <v>45561</v>
@@ -6363,7 +6363,7 @@
         <v>66</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C4" s="48">
         <v>45561</v>
@@ -6384,7 +6384,7 @@
         <v>67</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C5" s="48">
         <v>45561</v>
@@ -6393,7 +6393,7 @@
         <v>62</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="F5" s="25" t="s">
         <v>7</v>
@@ -6407,7 +6407,7 @@
         <v>68</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C6" s="48">
         <v>45561</v>
@@ -6416,7 +6416,7 @@
         <v>62</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="F6" s="25" t="s">
         <v>9</v>
@@ -6430,7 +6430,7 @@
         <v>69</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C7" s="48">
         <v>45561</v>
@@ -6439,7 +6439,7 @@
         <v>62</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="F7" s="25" t="s">
         <v>39</v>
@@ -6453,7 +6453,7 @@
         <v>70</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C8" s="48">
         <v>45561</v>
@@ -6462,7 +6462,7 @@
         <v>62</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="F8" s="25" t="s">
         <v>3</v>
@@ -6476,7 +6476,7 @@
         <v>71</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C9" s="48">
         <v>45561</v>
@@ -6485,7 +6485,7 @@
         <v>62</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="F9" s="25" t="s">
         <v>40</v>
@@ -6499,7 +6499,7 @@
         <v>72</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C10" s="48">
         <v>45561</v>
@@ -6508,7 +6508,7 @@
         <v>62</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="F10" s="25" t="s">
         <v>41</v>
@@ -6522,7 +6522,7 @@
         <v>73</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C11" s="48">
         <v>45561</v>
@@ -6543,7 +6543,7 @@
         <v>74</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C12" s="48">
         <v>45561</v>
@@ -6564,7 +6564,7 @@
         <v>75</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C13" s="48">
         <v>45561</v>
@@ -6585,7 +6585,7 @@
         <v>76</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C14" s="48">
         <v>45561</v>
@@ -6594,7 +6594,7 @@
         <v>62</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="F14" s="25" t="s">
         <v>45</v>
@@ -6608,7 +6608,7 @@
         <v>77</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C15" s="48">
         <v>45561</v>
@@ -6617,7 +6617,7 @@
         <v>62</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="F15" s="25" t="s">
         <v>46</v>
@@ -6631,7 +6631,7 @@
         <v>78</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C16" s="48">
         <v>45561</v>
@@ -6640,7 +6640,7 @@
         <v>62</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="F16" s="25" t="s">
         <v>47</v>
@@ -6654,7 +6654,7 @@
         <v>79</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C17" s="48">
         <v>45561</v>
@@ -6663,7 +6663,7 @@
         <v>62</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="F17" s="25" t="s">
         <v>48</v>
@@ -6677,7 +6677,7 @@
         <v>80</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C18" s="48">
         <v>45561</v>
@@ -6686,7 +6686,7 @@
         <v>62</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="F18" s="25" t="s">
         <v>49</v>
@@ -6700,7 +6700,7 @@
         <v>81</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C19" s="48">
         <v>45561</v>
@@ -6709,7 +6709,7 @@
         <v>62</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="F19" s="25" t="s">
         <v>50</v>
@@ -6723,7 +6723,7 @@
         <v>82</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C20" s="48">
         <v>45582</v>
@@ -6744,7 +6744,7 @@
         <v>83</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C21" s="48">
         <v>45582</v>
@@ -6765,7 +6765,7 @@
         <v>84</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C22" s="48">
         <v>45582</v>
@@ -6786,7 +6786,7 @@
         <v>85</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C23" s="48">
         <v>45582</v>
@@ -6795,7 +6795,7 @@
         <v>62</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="F23" s="25" t="s">
         <v>54</v>
@@ -6809,7 +6809,7 @@
         <v>86</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C24" s="48">
         <v>45582</v>
@@ -6818,7 +6818,7 @@
         <v>62</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="F24" s="25" t="s">
         <v>10</v>
@@ -6832,7 +6832,7 @@
         <v>87</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C25" s="48">
         <v>45582</v>
@@ -6841,7 +6841,7 @@
         <v>62</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="F25" s="25" t="s">
         <v>8</v>
@@ -6855,7 +6855,7 @@
         <v>88</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C26" s="48">
         <v>45582</v>
@@ -6864,7 +6864,7 @@
         <v>62</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="F26" s="25" t="s">
         <v>55</v>
@@ -6878,7 +6878,7 @@
         <v>89</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C27" s="48">
         <v>45582</v>
@@ -6887,7 +6887,7 @@
         <v>62</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="F27" s="25" t="s">
         <v>56</v>
@@ -6901,7 +6901,7 @@
         <v>90</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C28" s="51">
         <v>45582</v>
@@ -6910,7 +6910,7 @@
         <v>62</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="F28" s="53" t="s">
         <v>57</v>
